--- a/server/contactData.xlsx
+++ b/server/contactData.xlsx
@@ -462,6 +462,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/server/contactData.xlsx
+++ b/server/contactData.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="26">
   <si>
     <t>Name</t>
   </si>
@@ -28,19 +28,67 @@
     <t>Date</t>
   </si>
   <si>
-    <t>john</t>
-  </si>
-  <si>
-    <t>john@gmail.com</t>
-  </si>
-  <si>
-    <t>text</t>
-  </si>
-  <si>
-    <t>asdfghjzbcbferfb</t>
-  </si>
-  <si>
-    <t>17/10/2025, 5:42:21 pm</t>
+    <t>peter</t>
+  </si>
+  <si>
+    <t>peter@gmail.com</t>
+  </si>
+  <si>
+    <t>xcvbnfghj</t>
+  </si>
+  <si>
+    <t>ertyujbnhjb  cfgvhjb</t>
+  </si>
+  <si>
+    <t>27/10/2025, 5:01:10 pm</t>
+  </si>
+  <si>
+    <t>27/10/2025, 5:02:34 pm</t>
+  </si>
+  <si>
+    <t>rajbanni</t>
+  </si>
+  <si>
+    <t>rajbanni@gmail.com</t>
+  </si>
+  <si>
+    <t>jnjn kjnkm uii</t>
+  </si>
+  <si>
+    <t xml:space="preserve">injityhu gtyhutgyhugbh nnhjmujik </t>
+  </si>
+  <si>
+    <t>27/10/2025, 5:15:15 pm</t>
+  </si>
+  <si>
+    <t>hari</t>
+  </si>
+  <si>
+    <t>hari@gmail.com</t>
+  </si>
+  <si>
+    <t>vb</t>
+  </si>
+  <si>
+    <t>tygbvhjbgjb</t>
+  </si>
+  <si>
+    <t>27/10/2025, 5:17:43 pm</t>
+  </si>
+  <si>
+    <t>hwl</t>
+  </si>
+  <si>
+    <t>get@gmail.com</t>
+  </si>
+  <si>
+    <t>wert</t>
+  </si>
+  <si>
+    <t>wert edfg fgh</t>
+  </si>
+  <si>
+    <t>27/10/2025, 5:21:57 pm</t>
   </si>
 </sst>
 </file>
@@ -417,7 +465,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="2" width="30" customWidth="1"/>
@@ -460,8 +508,76 @@
         <v>9</v>
       </c>
     </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="s">
+        <v>23</v>
+      </c>
+      <c r="D6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" t="s">
+        <v>25</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>